--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748819</v>
       </c>
       <c r="B2" t="n">
-        <v>91751</v>
+        <v>91757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127748775</v>
       </c>
       <c r="B3" t="n">
-        <v>95802</v>
+        <v>95808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127748857</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748819</v>
       </c>
       <c r="B2" t="n">
-        <v>91757</v>
+        <v>91760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127748775</v>
       </c>
       <c r="B3" t="n">
-        <v>95808</v>
+        <v>95811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127748857</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748819</v>
       </c>
       <c r="B2" t="n">
-        <v>91760</v>
+        <v>91768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127748775</v>
       </c>
       <c r="B3" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127748857</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748819</v>
       </c>
       <c r="B2" t="n">
-        <v>91768</v>
+        <v>91769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127748775</v>
       </c>
       <c r="B3" t="n">
-        <v>95819</v>
+        <v>95820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127748857</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748819</v>
       </c>
       <c r="B2" t="n">
-        <v>91769</v>
+        <v>91770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127748775</v>
       </c>
       <c r="B3" t="n">
-        <v>95820</v>
+        <v>95821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127748857</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748819</v>
       </c>
       <c r="B2" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127748775</v>
       </c>
       <c r="B3" t="n">
-        <v>95821</v>
+        <v>95822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127748857</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748819</v>
       </c>
       <c r="B2" t="n">
-        <v>91771</v>
+        <v>91779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127748775</v>
       </c>
       <c r="B3" t="n">
-        <v>95822</v>
+        <v>95830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127748857</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748819</v>
       </c>
       <c r="B2" t="n">
-        <v>91779</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127748775</v>
       </c>
       <c r="B3" t="n">
-        <v>95830</v>
+        <v>95923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127748857</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1741,54 +1741,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>97530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R12" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,17 +1818,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,38 +1843,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B13" t="n">
-        <v>97530</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R13" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,13 +1936,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1741,38 +1741,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>97530</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R12" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,13 +1834,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,54 +1863,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R13" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,17 +1940,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129060862</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,54 +1741,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>97540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R12" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,17 +1818,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,38 +1843,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B13" t="n">
-        <v>97530</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R13" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,13 +1936,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,38 +1741,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>97540</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R12" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,13 +1834,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,54 +1863,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>97547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R13" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,17 +1940,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>129060862</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1741,54 +1741,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>97549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R12" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,17 +1818,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,38 +1843,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B13" t="n">
-        <v>97549</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R13" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,13 +1936,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,38 +1741,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>97549</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R12" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,13 +1834,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,54 +1863,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>97575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R13" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,17 +1940,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,54 +1741,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>97576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R12" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,17 +1818,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,38 +1843,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B13" t="n">
-        <v>97575</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R13" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,13 +1936,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,38 +1741,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>97576</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R12" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,13 +1834,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,54 +1863,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>97577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R13" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,17 +1940,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,54 +1741,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>97595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R12" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,17 +1818,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,38 +1843,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B13" t="n">
-        <v>97587</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R13" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,13 +1936,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1741,38 +1741,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129061110</v>
+        <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>97595</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562455</v>
+        <v>562463</v>
       </c>
       <c r="R12" t="n">
-        <v>6454152</v>
+        <v>6454131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,13 +1834,17 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,54 +1863,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060823</v>
+        <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>97595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562463</v>
+        <v>562455</v>
       </c>
       <c r="R13" t="n">
-        <v>6454131</v>
+        <v>6454152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,17 +1940,13 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>129060732</v>
       </c>
       <c r="B5" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129060764</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129060779</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>129060746</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129060877</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>129060716</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129061110</v>
       </c>
       <c r="B13" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129060788</v>
       </c>
       <c r="B14" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129101592</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>129060823</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127748819</v>
+        <v>127748775</v>
       </c>
       <c r="B2" t="n">
-        <v>91871</v>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562427</v>
+        <v>562463</v>
       </c>
       <c r="R2" t="n">
-        <v>6454138</v>
+        <v>6454139</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127748775</v>
+        <v>127748819</v>
       </c>
       <c r="B3" t="n">
-        <v>95923</v>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +788,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562463</v>
+        <v>562427</v>
       </c>
       <c r="R3" t="n">
-        <v>6454139</v>
+        <v>6454138</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,52 +878,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127748857</v>
+        <v>129101646</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Alserum/Tolen, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562473</v>
+        <v>562377</v>
       </c>
       <c r="R4" t="n">
-        <v>6454090</v>
+        <v>6454059</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,17 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>36 st</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,22 +967,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060732</v>
+        <v>129060823</v>
       </c>
       <c r="B5" t="n">
-        <v>105793</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,27 +990,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1024,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562371</v>
+        <v>562463</v>
       </c>
       <c r="R5" t="n">
-        <v>6454084</v>
+        <v>6454131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1074,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,7 +1083,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,52 +1101,72 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060764</v>
+        <v>127748799</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Alserum/Tolen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562389</v>
+        <v>562466</v>
       </c>
       <c r="R6" t="n">
-        <v>6454097</v>
+        <v>6454173</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,17 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,57 +1204,64 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060779</v>
+        <v>129060862</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1238,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562399</v>
+        <v>562420</v>
       </c>
       <c r="R7" t="n">
-        <v>6454092</v>
+        <v>6454113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,7 +1309,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Den äldre och till stora delar flerskiktad eskogen utgör en viktig del av talltitans hemvist och permanenta revir.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,7 +1318,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1306,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060746</v>
+        <v>127748857</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,17 +1371,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Alserum/Tolen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562378</v>
+        <v>562473</v>
       </c>
       <c r="R8" t="n">
-        <v>6454088</v>
+        <v>6454090</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,17 +1405,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ett trettiotal.</t>
+          <t>36 st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,22 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060877</v>
+        <v>129060716</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562434</v>
+        <v>562371</v>
       </c>
       <c r="R9" t="n">
-        <v>6454098</v>
+        <v>6454084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka små plantor som är lite svåra att upptäcka i mossan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060716</v>
+        <v>129060746</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562371</v>
+        <v>562378</v>
       </c>
       <c r="R10" t="n">
-        <v>6454084</v>
+        <v>6454088</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka små plantor som är lite svåra att upptäcka i mossan.</t>
+          <t>Ett trettiotal.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,46 +1657,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060862</v>
+        <v>129060764</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1674,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562420</v>
+        <v>562389</v>
       </c>
       <c r="R11" t="n">
-        <v>6454113</v>
+        <v>6454097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Den äldre och till stora delar flerskiktad eskogen utgör en viktig del av talltitans hemvist och permanenta revir.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,6 +1745,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1741,54 +1764,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060823</v>
+        <v>129060779</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562463</v>
+        <v>562399</v>
       </c>
       <c r="R12" t="n">
-        <v>6454131</v>
+        <v>6454092</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Den äldre granskogen respektive den angränsande tallmossen utgör en viktig del av spillkråkan revir.</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,6 +1852,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,32 +1871,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129061110</v>
+        <v>129060877</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562455</v>
+        <v>562434</v>
       </c>
       <c r="R13" t="n">
-        <v>6454152</v>
+        <v>6454098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,6 +1946,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,32 +1978,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060788</v>
+        <v>129101592</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562464</v>
+        <v>562376</v>
       </c>
       <c r="R14" t="n">
-        <v>6454110</v>
+        <v>6454074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,12 +2047,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,32 +2085,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101592</v>
+        <v>129060732</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>106243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562376</v>
+        <v>562371</v>
       </c>
       <c r="R15" t="n">
-        <v>6454074</v>
+        <v>6454084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,17 +2154,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,6 +2189,210 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129060788</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562464</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6454110</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129061110</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562455</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6454152</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34707-2025 artfynd.xlsx
+++ b/artfynd/A 34707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748775</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748819</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101646</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060823</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748799</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060862</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748857</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060716</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060746</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,6 +1811,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060764</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060779</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,6 +2035,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060877</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2082,6 +2147,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101592</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060732</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060788</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,8 +2473,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129061110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>